--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.0191837222411</v>
+        <v>10.24061735486418</v>
       </c>
       <c r="D2" t="n">
-        <v>61.02188453516245</v>
+        <v>9.916056236963898</v>
       </c>
       <c r="E2" t="n">
-        <v>9.478397709904488</v>
+        <v>1.54023962785948</v>
       </c>
       <c r="F2" t="n">
-        <v>10.07500791457705</v>
+        <v>1.637188786118771</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.13011407250193</v>
+        <v>10.25864353678156</v>
       </c>
       <c r="D3" t="n">
-        <v>61.29549498375393</v>
+        <v>9.960517934860015</v>
       </c>
       <c r="E3" t="n">
-        <v>9.478397709904488</v>
+        <v>1.54023962785948</v>
       </c>
       <c r="F3" t="n">
-        <v>10.07500791457705</v>
+        <v>1.637188786118771</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.51567257260537</v>
+        <v>7.721296793048372</v>
       </c>
       <c r="D4" t="n">
-        <v>46.85536956231873</v>
+        <v>7.613997553876794</v>
       </c>
       <c r="E4" t="n">
-        <v>9.478397709904488</v>
+        <v>1.54023962785948</v>
       </c>
       <c r="F4" t="n">
-        <v>10.07500791457705</v>
+        <v>1.637188786118771</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.18472988325566</v>
+        <v>10.10501860602905</v>
       </c>
       <c r="D5" t="n">
-        <v>63.04150750943345</v>
+        <v>10.24424497028294</v>
       </c>
       <c r="E5" t="n">
-        <v>9.478397709904488</v>
+        <v>1.54023962785948</v>
       </c>
       <c r="F5" t="n">
-        <v>10.07500791457705</v>
+        <v>1.637188786118771</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>64.00792146793279</v>
+        <v>10.40128723853908</v>
       </c>
       <c r="D6" t="n">
-        <v>65.64812645456152</v>
+        <v>10.66782054886625</v>
       </c>
       <c r="E6" t="n">
-        <v>9.478397709904488</v>
+        <v>1.54023962785948</v>
       </c>
       <c r="F6" t="n">
-        <v>10.07500791457705</v>
+        <v>1.637188786118771</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>80.30323611046757</v>
+        <v>13.04927586795098</v>
       </c>
       <c r="D7" t="n">
-        <v>80.4274429478471</v>
+        <v>13.06945947902515</v>
       </c>
       <c r="E7" t="n">
-        <v>9.478397709904488</v>
+        <v>1.54023962785948</v>
       </c>
       <c r="F7" t="n">
-        <v>10.07500791457705</v>
+        <v>1.637188786118771</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>62.55017722059733</v>
+        <v>10.16440379834707</v>
       </c>
       <c r="D8" t="n">
-        <v>64.50361942012597</v>
+        <v>10.48183815577047</v>
       </c>
       <c r="E8" t="n">
-        <v>9.478397709904488</v>
+        <v>1.54023962785948</v>
       </c>
       <c r="F8" t="n">
-        <v>10.07500791457705</v>
+        <v>1.637188786118771</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>77.51015010671325</v>
+        <v>12.59539939234091</v>
       </c>
       <c r="D9" t="n">
-        <v>79.54107983382195</v>
+        <v>12.92542547299607</v>
       </c>
       <c r="E9" t="n">
-        <v>9.478397709904488</v>
+        <v>1.54023962785948</v>
       </c>
       <c r="F9" t="n">
-        <v>10.07500791457705</v>
+        <v>1.637188786118771</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
